--- a/car_parts.xlsx
+++ b/car_parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mogumogu_gaming\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290AD8E2-543C-462C-8E9B-ABA090ACFFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F25C98A-C318-4F20-BDAC-CDADF267BA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{876C4246-E51A-4644-BFB5-379A27903F40}"/>
   </bookViews>
@@ -39,51 +39,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Part Name</t>
   </si>
   <si>
-    <t>Car Model</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
-    <t>Availability</t>
-  </si>
-  <si>
     <t>Brake Pads</t>
   </si>
   <si>
-    <t>Toyota Vios 2020</t>
-  </si>
-  <si>
-    <t>Available</t>
-  </si>
-  <si>
     <t>Oil Filter</t>
   </si>
   <si>
-    <t>Honda City 2019</t>
-  </si>
-  <si>
     <t>Air Filter</t>
   </si>
   <si>
-    <t>Toyota Innova 2021</t>
-  </si>
-  <si>
-    <t>Spark Plug</t>
-  </si>
-  <si>
-    <t>Cabin Filter</t>
-  </si>
-  <si>
-    <t>Out of Stock</t>
-  </si>
-  <si>
-    <t>Brake Disc</t>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Toyota</t>
+  </si>
+  <si>
+    <t>Vios</t>
+  </si>
+  <si>
+    <t>Honda</t>
+  </si>
+  <si>
+    <t>Civic</t>
   </si>
 </sst>
 </file>
@@ -469,109 +463,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0A252F-F097-454B-B8E0-AED1F592C484}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1500</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E3" s="2">
+        <v>450</v>
+      </c>
+      <c r="F3" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2500</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E4" s="2">
+        <v>650</v>
+      </c>
+      <c r="F4" s="2">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2">
-        <v>650</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2">
-        <v>900</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1200</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2">
-        <v>750</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2">
-        <v>4800</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
